--- a/Data/themes.xlsx
+++ b/Data/themes.xlsx
@@ -34,7 +34,7 @@
     <x:t>LogoPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Les Aigles - Football</x:t>
+    <x:t>Les Aigles</x:t>
   </x:si>
   <x:si>
     <x:t>#1a3a5c</x:t>
@@ -43,19 +43,19 @@
     <x:t>#e8a020</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/logos/d8519b05-3f5d-478c-b376-b99d8b0c8d03.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#f3e0be</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/logos/0d4aa1e9-3e17-4568-bee2-405c2635aa1c.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#92aac3</x:t>
+    <x:t>/uploads/logos/c2ee2f52-9f21-48d5-af4a-9f58c0f0181a.png</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cheerleader des aigles</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#d04343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#1d56dd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/logos/0fead71e-cfc7-4f57-8736-71a7f4180265.png</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -460,13 +460,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/themes.xlsx
+++ b/Data/themes.xlsx
@@ -43,19 +43,34 @@
     <x:t>#e8a020</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/logos/c2ee2f52-9f21-48d5-af4a-9f58c0f0181a.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cheerleader des aigles</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#d04343</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#1d56dd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/logos/0fead71e-cfc7-4f57-8736-71a7f4180265.png</x:t>
+    <x:t>/uploads/logos/b3846f9e-ee74-40e1-a942-b7c00daaeacd.png</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/musique/34d185d7-e8b0-4308-8cda-b75e7244f8d3.mp3</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Aigles 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/logos/4fe7e7a5-a8f9-40dc-9864-9561e71fc1ed.png</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Scorpions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/logos/36e43e60-a60e-497c-95d7-538b6f6665f7.avif</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#4087d4</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -409,7 +424,7 @@
   <x:dimension ref="A1:F1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:15">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -429,7 +444,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
+    <x:row r="2" spans="1:15">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -448,8 +463,35 @@
       <x:c r="F2" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
     </x:row>
-    <x:row r="3" spans="1:6">
+    <x:row r="3" spans="1:15">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -457,15 +499,89 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
